--- a/اسماء شركات الاسنان/Tosyali_List (2).xlsx
+++ b/اسماء شركات الاسنان/Tosyali_List (2).xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Desktop\بطاقات\TOSY CARD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Omar\waad_temp_website\اسماء شركات الاسنان\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B956B4AA-DB67-4F8D-B568-9C579D6BD299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="3" r:id="rId1"/>
@@ -19,17 +20,26 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">'1'!$A$1:$F$32</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'1'!$1:$1</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1476" uniqueCount="542">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1477" uniqueCount="543">
   <si>
     <t>يسري سعيد المغربي</t>
   </si>
@@ -1655,12 +1665,15 @@
   </si>
   <si>
     <t>TOSY202500101D2</t>
+  </si>
+  <si>
+    <t>Column2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
@@ -1669,7 +1682,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="178"/>
       <scheme val="minor"/>
@@ -1677,7 +1690,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1685,13 +1698,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="178"/>
       <scheme val="minor"/>
@@ -1714,14 +1727,14 @@
       <b/>
       <sz val="18"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="18"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1729,7 +1742,7 @@
       <b/>
       <sz val="18"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1737,7 +1750,7 @@
       <b/>
       <sz val="18"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1749,7 +1762,7 @@
     <font>
       <sz val="16"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="178"/>
       <scheme val="minor"/>
@@ -1757,7 +1770,7 @@
     <font>
       <sz val="18"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="178"/>
       <scheme val="minor"/>
@@ -1766,21 +1779,21 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="28"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="48"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2124,7 +2137,7 @@
     <xf numFmtId="165" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2200,24 +2213,6 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2260,11 +2255,29 @@
     <xf numFmtId="14" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="21">
+  <dxfs count="22">
     <dxf>
       <font>
         <b/>
@@ -2273,14 +2286,14 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color theme="1"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
         <name val="Calibri"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor theme="0"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2497,6 +2510,26 @@
           <color auto="1"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -2949,32 +2982,33 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="الجدول13" displayName="الجدول13" ref="B1:G259" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
-  <autoFilter ref="B1:G259"/>
-  <tableColumns count="6">
-    <tableColumn id="1" name="Name" dataDxfId="18" totalsRowDxfId="17"/>
-    <tableColumn id="2" name="DOB" dataDxfId="16" totalsRowDxfId="15"/>
-    <tableColumn id="3" name="Status" dataDxfId="14" totalsRowDxfId="13"/>
-    <tableColumn id="5" name="Status2" dataDxfId="12" totalsRowDxfId="11"/>
-    <tableColumn id="4" name="Insurance Profile" dataDxfId="10" totalsRowDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="الجدول13" displayName="الجدول13" ref="B1:H259" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
+  <autoFilter ref="B1:H259" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Name" dataDxfId="19" totalsRowDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="DOB" dataDxfId="17" totalsRowDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Status" dataDxfId="15" totalsRowDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Status2" dataDxfId="13" totalsRowDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Insurance Profile" dataDxfId="11" totalsRowDxfId="10">
       <calculatedColumnFormula>الجدول13[[#This Row],[Column1]]&amp;""&amp;A2&amp;الجدول13[[#This Row],[Status]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" name="Column1" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Column1" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{5AA751BB-6099-4D0B-9100-D6E3C852C34C}" name="Column2" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="الجدول1" displayName="الجدول1" ref="B312:G370" totalsRowShown="0" headerRowDxfId="7" dataDxfId="0">
-  <autoFilter ref="B312:G370"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="الجدول1" displayName="الجدول1" ref="B312:G370" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+  <autoFilter ref="B312:G370" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="الاســـــــــــم" dataDxfId="6"/>
-    <tableColumn id="2" name="تاريخ الميلاد" dataDxfId="5"/>
-    <tableColumn id="5" name="الصفة" dataDxfId="4"/>
-    <tableColumn id="8" name="الرقم التسلسلي" dataDxfId="3"/>
-    <tableColumn id="3" name="Column1" dataDxfId="2"/>
-    <tableColumn id="6" name="ملاحظـــــــــــــــــــات" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="الاســـــــــــم" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="تاريخ الميلاد" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="الصفة" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="الرقم التسلسلي" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Column1" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="ملاحظـــــــــــــــــــات" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3276,22 +3310,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K371"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="23.25" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="22.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.85546875" style="19" customWidth="1"/>
-    <col min="2" max="2" width="56.7109375" style="19" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.28515625" style="19" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" style="19" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.28515625" style="19" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.8984375" style="19" customWidth="1"/>
+    <col min="2" max="2" width="56.69921875" style="19" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.296875" style="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.59765625" style="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.296875" style="19" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="48" style="19" customWidth="1"/>
-    <col min="7" max="7" width="28.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.7109375" customWidth="1"/>
-    <col min="9" max="9" width="17.140625" customWidth="1"/>
+    <col min="7" max="7" width="28.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.69921875" customWidth="1"/>
+    <col min="9" max="9" width="17.09765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="2" customFormat="1" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" s="2" customFormat="1" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>288</v>
       </c>
@@ -3313,8 +3347,11 @@
       <c r="G1" s="3" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H1" s="3" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="9">
         <v>1</v>
       </c>
@@ -3335,12 +3372,14 @@
       <c r="G2" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="H2" s="1"/>
+      <c r="H2" s="29">
+        <v>1</v>
+      </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
     </row>
-    <row r="3" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="9">
         <v>1</v>
       </c>
@@ -3363,12 +3402,14 @@
       <c r="G3" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="H3" s="1"/>
+      <c r="H3" s="29">
+        <v>2</v>
+      </c>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
     </row>
-    <row r="4" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="9">
         <v>1</v>
       </c>
@@ -3391,12 +3432,14 @@
       <c r="G4" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="H4" s="1"/>
+      <c r="H4" s="29">
+        <v>3</v>
+      </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
     </row>
-    <row r="5" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="9">
         <v>1</v>
       </c>
@@ -3419,12 +3462,14 @@
       <c r="G5" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="H5" s="1"/>
+      <c r="H5" s="29">
+        <v>4</v>
+      </c>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
     </row>
-    <row r="6" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="9">
         <v>1</v>
       </c>
@@ -3447,12 +3492,14 @@
       <c r="G6" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="H6" s="1"/>
+      <c r="H6" s="29">
+        <v>5</v>
+      </c>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
     </row>
-    <row r="7" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="9">
         <v>1</v>
       </c>
@@ -3475,12 +3522,14 @@
       <c r="G7" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="H7" s="1"/>
+      <c r="H7" s="29">
+        <v>6</v>
+      </c>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
     </row>
-    <row r="8" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="9">
         <v>1</v>
       </c>
@@ -3503,12 +3552,14 @@
       <c r="G8" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="H8" s="1"/>
+      <c r="H8" s="29">
+        <v>7</v>
+      </c>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
     </row>
-    <row r="9" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="9">
         <v>2</v>
       </c>
@@ -3529,12 +3580,14 @@
       <c r="G9" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="H9" s="1"/>
+      <c r="H9" s="29">
+        <v>8</v>
+      </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
     </row>
-    <row r="10" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="9">
         <v>2</v>
       </c>
@@ -3557,12 +3610,14 @@
       <c r="G10" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="H10" s="1"/>
+      <c r="H10" s="29">
+        <v>9</v>
+      </c>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
     </row>
-    <row r="11" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="9">
         <v>2</v>
       </c>
@@ -3585,12 +3640,14 @@
       <c r="G11" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="H11" s="1"/>
+      <c r="H11" s="29">
+        <v>10</v>
+      </c>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
     </row>
-    <row r="12" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="9">
         <v>2</v>
       </c>
@@ -3613,12 +3670,14 @@
       <c r="G12" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="H12" s="1"/>
+      <c r="H12" s="29">
+        <v>11</v>
+      </c>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
     </row>
-    <row r="13" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="9">
         <v>2</v>
       </c>
@@ -3641,12 +3700,14 @@
       <c r="G13" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="H13" s="1"/>
+      <c r="H13" s="29">
+        <v>12</v>
+      </c>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
     </row>
-    <row r="14" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="9">
         <v>3</v>
       </c>
@@ -3667,8 +3728,11 @@
       <c r="G14" s="5" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H14" s="29">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="9">
         <v>3</v>
       </c>
@@ -3691,8 +3755,11 @@
       <c r="G15" s="5" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H15" s="29">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="9">
         <v>3</v>
       </c>
@@ -3715,8 +3782,11 @@
       <c r="G16" s="5" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H16" s="29">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="9">
         <v>3</v>
       </c>
@@ -3739,8 +3809,11 @@
       <c r="G17" s="5" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H17" s="29">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="9">
         <v>3</v>
       </c>
@@ -3763,8 +3836,11 @@
       <c r="G18" s="5" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H18" s="29">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="9">
         <v>3</v>
       </c>
@@ -3787,8 +3863,11 @@
       <c r="G19" s="5" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H19" s="29">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="9">
         <v>4</v>
       </c>
@@ -3809,8 +3888,11 @@
       <c r="G20" s="5" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H20" s="29">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="9">
         <v>4</v>
       </c>
@@ -3833,8 +3915,11 @@
       <c r="G21" s="5" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H21" s="29">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="9">
         <v>4</v>
       </c>
@@ -3857,8 +3942,11 @@
       <c r="G22" s="5" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H22" s="29">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="9">
         <v>5</v>
       </c>
@@ -3879,8 +3967,11 @@
       <c r="G23" s="5" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H23" s="29">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="9">
         <v>5</v>
       </c>
@@ -3903,8 +3994,11 @@
       <c r="G24" s="5" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H24" s="29">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="9">
         <v>5</v>
       </c>
@@ -3927,8 +4021,11 @@
       <c r="G25" s="5" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H25" s="29">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="9">
         <v>5</v>
       </c>
@@ -3951,8 +4048,11 @@
       <c r="G26" s="5" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H26" s="29">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="9">
         <v>5</v>
       </c>
@@ -3975,8 +4075,11 @@
       <c r="G27" s="5" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H27" s="29">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="9">
         <v>6</v>
       </c>
@@ -3997,12 +4100,14 @@
       <c r="G28" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="H28" s="1"/>
+      <c r="H28" s="29">
+        <v>27</v>
+      </c>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
     </row>
-    <row r="29" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="9">
         <v>6</v>
       </c>
@@ -4025,12 +4130,14 @@
       <c r="G29" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="H29" s="1"/>
+      <c r="H29" s="29">
+        <v>28</v>
+      </c>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
     </row>
-    <row r="30" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="9">
         <v>6</v>
       </c>
@@ -4053,12 +4160,14 @@
       <c r="G30" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="H30" s="1"/>
+      <c r="H30" s="29">
+        <v>29</v>
+      </c>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
     </row>
-    <row r="31" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="9">
         <v>7</v>
       </c>
@@ -4079,8 +4188,11 @@
       <c r="G31" s="5" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H31" s="29">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="9">
         <v>7</v>
       </c>
@@ -4103,8 +4215,11 @@
       <c r="G32" s="5" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H32" s="29">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="9">
         <v>8</v>
       </c>
@@ -4125,8 +4240,11 @@
       <c r="G33" s="5" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H33" s="29">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="9">
         <v>8</v>
       </c>
@@ -4149,8 +4267,11 @@
       <c r="G34" s="5" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H34" s="29">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="9">
         <v>8</v>
       </c>
@@ -4173,8 +4294,11 @@
       <c r="G35" s="5" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H35" s="29">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="9">
         <v>8</v>
       </c>
@@ -4197,8 +4321,11 @@
       <c r="G36" s="5" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H36" s="29">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="9">
         <v>8</v>
       </c>
@@ -4221,8 +4348,11 @@
       <c r="G37" s="5" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H37" s="29">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="9">
         <v>8</v>
       </c>
@@ -4245,8 +4375,11 @@
       <c r="G38" s="5" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H38" s="29">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="9">
         <v>8</v>
       </c>
@@ -4269,8 +4402,11 @@
       <c r="G39" s="5" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H39" s="29">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="9">
         <v>8</v>
       </c>
@@ -4293,8 +4429,11 @@
       <c r="G40" s="5" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H40" s="29">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="9">
         <v>9</v>
       </c>
@@ -4315,8 +4454,11 @@
       <c r="G41" s="5" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H41" s="29">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="9">
         <v>9</v>
       </c>
@@ -4339,8 +4481,11 @@
       <c r="G42" s="5" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H42" s="29">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="9">
         <v>9</v>
       </c>
@@ -4363,8 +4508,11 @@
       <c r="G43" s="5" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H43" s="29">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="9">
         <v>9</v>
       </c>
@@ -4387,8 +4535,11 @@
       <c r="G44" s="5" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H44" s="29">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="9">
         <v>9</v>
       </c>
@@ -4411,8 +4562,11 @@
       <c r="G45" s="5" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H45" s="29">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="9">
         <v>9</v>
       </c>
@@ -4435,8 +4589,11 @@
       <c r="G46" s="5" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H46" s="29">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="9">
         <v>10</v>
       </c>
@@ -4457,8 +4614,11 @@
       <c r="G47" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H47" s="29">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="9">
         <v>10</v>
       </c>
@@ -4481,8 +4641,11 @@
       <c r="G48" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H48" s="29">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="9">
         <v>10</v>
       </c>
@@ -4505,8 +4668,11 @@
       <c r="G49" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H49" s="29">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="9">
         <v>12</v>
       </c>
@@ -4527,8 +4693,11 @@
       <c r="G50" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H50" s="29">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="9">
         <v>12</v>
       </c>
@@ -4551,8 +4720,11 @@
       <c r="G51" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H51" s="29">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="9">
         <v>13</v>
       </c>
@@ -4573,8 +4745,11 @@
       <c r="G52" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H52" s="29">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="9">
         <v>13</v>
       </c>
@@ -4597,8 +4772,11 @@
       <c r="G53" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H53" s="29">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="9">
         <v>13</v>
       </c>
@@ -4621,8 +4799,11 @@
       <c r="G54" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H54" s="29">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="9">
         <v>13</v>
       </c>
@@ -4645,8 +4826,11 @@
       <c r="G55" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H55" s="29">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="9">
         <v>13</v>
       </c>
@@ -4669,8 +4853,11 @@
       <c r="G56" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H56" s="29">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="9">
         <v>13</v>
       </c>
@@ -4693,8 +4880,11 @@
       <c r="G57" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H57" s="29">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="9">
         <v>14</v>
       </c>
@@ -4715,8 +4905,11 @@
       <c r="G58" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H58" s="29">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="9">
         <v>14</v>
       </c>
@@ -4739,8 +4932,11 @@
       <c r="G59" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H59" s="29">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="9">
         <v>14</v>
       </c>
@@ -4763,8 +4959,11 @@
       <c r="G60" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H60" s="29">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="9">
         <v>14</v>
       </c>
@@ -4787,8 +4986,11 @@
       <c r="G61" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H61" s="29">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="9">
         <v>14</v>
       </c>
@@ -4811,8 +5013,11 @@
       <c r="G62" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H62" s="29">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="9">
         <v>14</v>
       </c>
@@ -4835,8 +5040,11 @@
       <c r="G63" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H63" s="29">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="9">
         <v>14</v>
       </c>
@@ -4859,8 +5067,11 @@
       <c r="G64" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H64" s="29">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="9">
         <v>14</v>
       </c>
@@ -4883,8 +5094,11 @@
       <c r="G65" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H65" s="29">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="9">
         <v>14</v>
       </c>
@@ -4907,8 +5121,11 @@
       <c r="G66" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="67" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H66" s="29">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="9">
         <v>15</v>
       </c>
@@ -4929,8 +5146,11 @@
       <c r="G67" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H67" s="29">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="9">
         <v>15</v>
       </c>
@@ -4953,8 +5173,11 @@
       <c r="G68" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H68" s="29">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="9">
         <v>16</v>
       </c>
@@ -4975,8 +5198,11 @@
       <c r="G69" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="70" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H69" s="29">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="9">
         <v>16</v>
       </c>
@@ -4999,8 +5225,11 @@
       <c r="G70" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H70" s="29">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="9">
         <v>16</v>
       </c>
@@ -5023,8 +5252,11 @@
       <c r="G71" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="72" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H71" s="29">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="9">
         <v>17</v>
       </c>
@@ -5045,8 +5277,11 @@
       <c r="G72" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="73" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H72" s="29">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="9">
         <v>17</v>
       </c>
@@ -5069,8 +5304,11 @@
       <c r="G73" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="74" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H73" s="29">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="9">
         <v>17</v>
       </c>
@@ -5093,8 +5331,11 @@
       <c r="G74" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="75" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H74" s="29">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="9">
         <v>18</v>
       </c>
@@ -5115,8 +5356,11 @@
       <c r="G75" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="76" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H75" s="29">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="9">
         <v>18</v>
       </c>
@@ -5139,8 +5383,11 @@
       <c r="G76" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="77" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H76" s="29">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="9">
         <v>18</v>
       </c>
@@ -5163,8 +5410,11 @@
       <c r="G77" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="78" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H77" s="29">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="9">
         <v>18</v>
       </c>
@@ -5187,8 +5437,11 @@
       <c r="G78" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="79" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H78" s="29">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="9">
         <v>18</v>
       </c>
@@ -5211,8 +5464,11 @@
       <c r="G79" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="80" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H79" s="29">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="9">
         <v>18</v>
       </c>
@@ -5235,8 +5491,11 @@
       <c r="G80" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="81" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H80" s="29">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="9">
         <v>19</v>
       </c>
@@ -5257,8 +5516,11 @@
       <c r="G81" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="82" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H81" s="29">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="9">
         <v>19</v>
       </c>
@@ -5281,8 +5543,11 @@
       <c r="G82" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="83" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H82" s="29">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="9">
         <v>19</v>
       </c>
@@ -5305,8 +5570,11 @@
       <c r="G83" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="84" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H83" s="29">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="9">
         <v>20</v>
       </c>
@@ -5327,8 +5595,11 @@
       <c r="G84" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="85" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H84" s="29">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="9">
         <v>20</v>
       </c>
@@ -5351,8 +5622,11 @@
       <c r="G85" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="86" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H85" s="29">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="9">
         <v>20</v>
       </c>
@@ -5375,8 +5649,11 @@
       <c r="G86" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="87" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H86" s="29">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="9">
         <v>21</v>
       </c>
@@ -5397,8 +5674,11 @@
       <c r="G87" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="88" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H87" s="29">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="9">
         <v>21</v>
       </c>
@@ -5421,8 +5701,11 @@
       <c r="G88" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="89" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H88" s="29">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="9">
         <v>22</v>
       </c>
@@ -5443,8 +5726,11 @@
       <c r="G89" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="90" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H89" s="29">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="9">
         <v>22</v>
       </c>
@@ -5467,8 +5753,11 @@
       <c r="G90" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="91" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H90" s="29">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="9">
         <v>22</v>
       </c>
@@ -5491,8 +5780,11 @@
       <c r="G91" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="92" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H91" s="29">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="9">
         <v>22</v>
       </c>
@@ -5515,8 +5807,11 @@
       <c r="G92" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="93" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H92" s="29">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" s="9">
         <v>22</v>
       </c>
@@ -5539,8 +5834,11 @@
       <c r="G93" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="94" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H93" s="29">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A94" s="9">
         <v>23</v>
       </c>
@@ -5561,8 +5859,11 @@
       <c r="G94" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="95" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H94" s="29">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A95" s="9">
         <v>23</v>
       </c>
@@ -5585,8 +5886,11 @@
       <c r="G95" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="96" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H95" s="29">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A96" s="9">
         <v>23</v>
       </c>
@@ -5609,8 +5913,11 @@
       <c r="G96" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="97" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H96" s="29">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A97" s="9">
         <v>25</v>
       </c>
@@ -5631,8 +5938,11 @@
       <c r="G97" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="98" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H97" s="29">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A98" s="9">
         <v>25</v>
       </c>
@@ -5655,8 +5965,11 @@
       <c r="G98" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="99" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H98" s="29">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A99" s="9">
         <v>25</v>
       </c>
@@ -5679,8 +5992,11 @@
       <c r="G99" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="100" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H99" s="29">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A100" s="9">
         <v>26</v>
       </c>
@@ -5701,8 +6017,11 @@
       <c r="G100" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="101" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H100" s="29">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A101" s="9">
         <v>26</v>
       </c>
@@ -5725,8 +6044,11 @@
       <c r="G101" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="102" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H101" s="29">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A102" s="9">
         <v>26</v>
       </c>
@@ -5749,8 +6071,11 @@
       <c r="G102" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="103" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H102" s="29">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A103" s="9">
         <v>26</v>
       </c>
@@ -5773,8 +6098,11 @@
       <c r="G103" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="104" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H103" s="29">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A104" s="9">
         <v>266</v>
       </c>
@@ -5795,8 +6123,11 @@
       <c r="G104" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="105" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H104" s="29">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A105" s="9">
         <v>266</v>
       </c>
@@ -5819,8 +6150,11 @@
       <c r="G105" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="106" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H105" s="29">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A106" s="9">
         <v>266</v>
       </c>
@@ -5843,8 +6177,11 @@
       <c r="G106" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="107" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H106" s="29">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A107" s="9">
         <v>27</v>
       </c>
@@ -5865,8 +6202,11 @@
       <c r="G107" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="108" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H107" s="29">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A108" s="9">
         <v>27</v>
       </c>
@@ -5889,8 +6229,11 @@
       <c r="G108" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="109" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H108" s="29">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A109" s="9">
         <v>27</v>
       </c>
@@ -5913,8 +6256,11 @@
       <c r="G109" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="110" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H109" s="29">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A110" s="9">
         <v>28</v>
       </c>
@@ -5935,8 +6281,11 @@
       <c r="G110" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="111" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H110" s="29">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A111" s="9">
         <v>28</v>
       </c>
@@ -5959,8 +6308,11 @@
       <c r="G111" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="112" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H111" s="29">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A112" s="9">
         <v>28</v>
       </c>
@@ -5983,8 +6335,11 @@
       <c r="G112" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="113" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H112" s="29">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A113" s="9">
         <v>28</v>
       </c>
@@ -6007,8 +6362,11 @@
       <c r="G113" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="114" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H113" s="29">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A114" s="9">
         <v>29</v>
       </c>
@@ -6029,8 +6387,11 @@
       <c r="G114" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="115" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H114" s="29">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A115" s="9">
         <v>29</v>
       </c>
@@ -6053,8 +6414,11 @@
       <c r="G115" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="116" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H115" s="29">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A116" s="9">
         <v>29</v>
       </c>
@@ -6077,8 +6441,11 @@
       <c r="G116" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="117" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H116" s="29">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A117" s="9">
         <v>29</v>
       </c>
@@ -6101,8 +6468,11 @@
       <c r="G117" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="118" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H117" s="29">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A118" s="9">
         <v>29</v>
       </c>
@@ -6125,8 +6495,11 @@
       <c r="G118" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="119" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H118" s="29">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A119" s="9">
         <v>30</v>
       </c>
@@ -6147,8 +6520,11 @@
       <c r="G119" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="120" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H119" s="29">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A120" s="9">
         <v>30</v>
       </c>
@@ -6171,8 +6547,11 @@
       <c r="G120" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="121" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H120" s="29">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A121" s="9">
         <v>30</v>
       </c>
@@ -6195,8 +6574,11 @@
       <c r="G121" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="122" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H121" s="29">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A122" s="9">
         <v>30</v>
       </c>
@@ -6219,8 +6601,11 @@
       <c r="G122" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="123" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H122" s="29">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A123" s="9">
         <v>31</v>
       </c>
@@ -6241,8 +6626,11 @@
       <c r="G123" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="124" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H123" s="29">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A124" s="9">
         <v>31</v>
       </c>
@@ -6265,8 +6653,11 @@
       <c r="G124" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="125" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H124" s="29">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A125" s="9">
         <v>31</v>
       </c>
@@ -6289,8 +6680,11 @@
       <c r="G125" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="126" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H125" s="29">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A126" s="9">
         <v>32</v>
       </c>
@@ -6311,8 +6705,11 @@
       <c r="G126" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="127" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H126" s="29">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A127" s="9">
         <v>32</v>
       </c>
@@ -6335,8 +6732,11 @@
       <c r="G127" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="128" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H127" s="29">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A128" s="9">
         <v>33</v>
       </c>
@@ -6357,8 +6757,11 @@
       <c r="G128" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="129" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H128" s="29">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A129" s="9">
         <v>33</v>
       </c>
@@ -6381,8 +6784,11 @@
       <c r="G129" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="130" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H129" s="29">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A130" s="9">
         <v>33</v>
       </c>
@@ -6405,8 +6811,11 @@
       <c r="G130" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="131" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H130" s="29">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A131" s="9">
         <v>33</v>
       </c>
@@ -6429,8 +6838,11 @@
       <c r="G131" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="132" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H131" s="29">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A132" s="9">
         <v>33</v>
       </c>
@@ -6453,8 +6865,11 @@
       <c r="G132" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="133" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H132" s="29">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A133" s="9">
         <v>33</v>
       </c>
@@ -6477,8 +6892,11 @@
       <c r="G133" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="134" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H133" s="29">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A134" s="9">
         <v>33</v>
       </c>
@@ -6501,8 +6919,11 @@
       <c r="G134" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="135" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H134" s="29">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A135" s="9">
         <v>33</v>
       </c>
@@ -6522,8 +6943,11 @@
         <v>290</v>
       </c>
       <c r="G135" s="29"/>
-    </row>
-    <row r="136" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H135" s="29">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A136" s="9">
         <v>34</v>
       </c>
@@ -6544,8 +6968,11 @@
       <c r="G136" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="137" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H136" s="29">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A137" s="9">
         <v>34</v>
       </c>
@@ -6568,8 +6995,11 @@
       <c r="G137" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="138" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H137" s="29">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A138" s="9">
         <v>34</v>
       </c>
@@ -6592,8 +7022,11 @@
       <c r="G138" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="139" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H138" s="29">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A139" s="9">
         <v>34</v>
       </c>
@@ -6616,8 +7049,11 @@
       <c r="G139" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="140" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H139" s="29">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A140" s="9">
         <v>34</v>
       </c>
@@ -6640,8 +7076,11 @@
       <c r="G140" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="141" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H140" s="29">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A141" s="9">
         <v>35</v>
       </c>
@@ -6662,8 +7101,11 @@
       <c r="G141" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="142" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H141" s="29">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A142" s="9">
         <v>35</v>
       </c>
@@ -6686,8 +7128,11 @@
       <c r="G142" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="143" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H142" s="29">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A143" s="9">
         <v>35</v>
       </c>
@@ -6710,8 +7155,11 @@
       <c r="G143" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="144" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H143" s="29">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A144" s="9">
         <v>36</v>
       </c>
@@ -6732,8 +7180,11 @@
       <c r="G144" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="145" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H144" s="29">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A145" s="9">
         <v>36</v>
       </c>
@@ -6756,8 +7207,11 @@
       <c r="G145" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="146" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H145" s="29">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A146" s="9">
         <v>36</v>
       </c>
@@ -6780,8 +7234,11 @@
       <c r="G146" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="147" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H146" s="29">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A147" s="9">
         <v>36</v>
       </c>
@@ -6804,8 +7261,11 @@
       <c r="G147" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="148" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H147" s="29">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A148" s="9">
         <v>36</v>
       </c>
@@ -6828,8 +7288,11 @@
       <c r="G148" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="149" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H148" s="29">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A149" s="9">
         <v>36</v>
       </c>
@@ -6852,8 +7315,11 @@
       <c r="G149" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="150" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H149" s="29">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A150" s="9">
         <v>36</v>
       </c>
@@ -6876,8 +7342,11 @@
       <c r="G150" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="151" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H150" s="29">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A151" s="9">
         <v>37</v>
       </c>
@@ -6898,8 +7367,11 @@
       <c r="G151" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="152" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H151" s="29">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A152" s="9">
         <v>37</v>
       </c>
@@ -6922,8 +7394,11 @@
       <c r="G152" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="153" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H152" s="29">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A153" s="9">
         <v>37</v>
       </c>
@@ -6946,8 +7421,11 @@
       <c r="G153" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="154" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H153" s="29">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A154" s="9">
         <v>38</v>
       </c>
@@ -6968,8 +7446,11 @@
       <c r="G154" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="155" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H154" s="29">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A155" s="9">
         <v>38</v>
       </c>
@@ -6992,8 +7473,11 @@
       <c r="G155" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="156" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H155" s="29">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A156" s="9">
         <v>38</v>
       </c>
@@ -7016,8 +7500,11 @@
       <c r="G156" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="157" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H156" s="29">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A157" s="9">
         <v>39</v>
       </c>
@@ -7038,8 +7525,11 @@
       <c r="G157" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="158" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H157" s="29">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A158" s="9">
         <v>39</v>
       </c>
@@ -7062,8 +7552,11 @@
       <c r="G158" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="159" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H158" s="29">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A159" s="9">
         <v>40</v>
       </c>
@@ -7084,8 +7577,11 @@
       <c r="G159" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="160" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H159" s="29">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A160" s="9">
         <v>40</v>
       </c>
@@ -7108,8 +7604,11 @@
       <c r="G160" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="161" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H160" s="29">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A161" s="9">
         <v>40</v>
       </c>
@@ -7132,8 +7631,11 @@
       <c r="G161" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="162" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H161" s="29">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A162" s="9">
         <v>40</v>
       </c>
@@ -7156,8 +7658,11 @@
       <c r="G162" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="163" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H162" s="29">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A163" s="9">
         <v>40</v>
       </c>
@@ -7180,8 +7685,11 @@
       <c r="G163" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="164" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H163" s="29">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A164" s="9">
         <v>41</v>
       </c>
@@ -7202,8 +7710,11 @@
       <c r="G164" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="165" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H164" s="29">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A165" s="9">
         <v>41</v>
       </c>
@@ -7226,8 +7737,11 @@
       <c r="G165" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="166" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H165" s="29">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A166" s="9">
         <v>41</v>
       </c>
@@ -7250,8 +7764,11 @@
       <c r="G166" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="167" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H166" s="29">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A167" s="9">
         <v>41</v>
       </c>
@@ -7274,8 +7791,11 @@
       <c r="G167" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="168" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H167" s="29">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A168" s="9">
         <v>41</v>
       </c>
@@ -7298,8 +7818,11 @@
       <c r="G168" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="169" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H168" s="29">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A169" s="9">
         <v>41</v>
       </c>
@@ -7322,8 +7845,11 @@
       <c r="G169" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="170" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H169" s="29">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A170" s="9">
         <v>42</v>
       </c>
@@ -7344,8 +7870,11 @@
       <c r="G170" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="171" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H170" s="29">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A171" s="9">
         <v>42</v>
       </c>
@@ -7368,8 +7897,11 @@
       <c r="G171" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="172" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H171" s="29">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A172" s="9">
         <v>42</v>
       </c>
@@ -7392,8 +7924,11 @@
       <c r="G172" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="173" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H172" s="29">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A173" s="9">
         <v>42</v>
       </c>
@@ -7416,8 +7951,11 @@
       <c r="G173" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="174" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H173" s="29">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A174" s="9">
         <v>42</v>
       </c>
@@ -7440,8 +7978,11 @@
       <c r="G174" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="175" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H174" s="29">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A175" s="9">
         <v>42</v>
       </c>
@@ -7464,8 +8005,11 @@
       <c r="G175" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="176" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H175" s="29">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A176" s="9">
         <v>42</v>
       </c>
@@ -7488,8 +8032,11 @@
       <c r="G176" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="177" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H176" s="29">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A177" s="9">
         <v>42</v>
       </c>
@@ -7512,8 +8059,11 @@
       <c r="G177" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="178" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H177" s="29">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A178" s="9">
         <v>42</v>
       </c>
@@ -7536,8 +8086,11 @@
       <c r="G178" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="179" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H178" s="29">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A179" s="9">
         <v>43</v>
       </c>
@@ -7558,8 +8111,11 @@
       <c r="G179" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="180" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H179" s="29">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A180" s="9">
         <v>43</v>
       </c>
@@ -7582,8 +8138,11 @@
       <c r="G180" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="181" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H180" s="29">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A181" s="9">
         <v>44</v>
       </c>
@@ -7604,8 +8163,11 @@
       <c r="G181" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="182" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H181" s="29">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A182" s="9">
         <v>44</v>
       </c>
@@ -7628,8 +8190,11 @@
       <c r="G182" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="183" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H182" s="29">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A183" s="9">
         <v>44</v>
       </c>
@@ -7652,8 +8217,11 @@
       <c r="G183" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="184" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H183" s="29">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A184" s="9">
         <v>44</v>
       </c>
@@ -7676,8 +8244,11 @@
       <c r="G184" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="185" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H184" s="29">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A185" s="9">
         <v>44</v>
       </c>
@@ -7700,8 +8271,11 @@
       <c r="G185" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="186" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H185" s="29">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A186" s="9">
         <v>44</v>
       </c>
@@ -7724,8 +8298,11 @@
       <c r="G186" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="187" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H186" s="29">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A187" s="9">
         <v>44</v>
       </c>
@@ -7748,8 +8325,11 @@
       <c r="G187" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="188" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H187" s="29">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A188" s="9">
         <v>44</v>
       </c>
@@ -7772,8 +8352,11 @@
       <c r="G188" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="189" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H188" s="29">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A189" s="9">
         <v>44</v>
       </c>
@@ -7796,8 +8379,11 @@
       <c r="G189" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="190" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H189" s="29">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A190" s="9">
         <v>45</v>
       </c>
@@ -7818,8 +8404,11 @@
       <c r="G190" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="191" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H190" s="29">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A191" s="9">
         <v>45</v>
       </c>
@@ -7842,8 +8431,11 @@
       <c r="G191" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="192" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H191" s="29">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A192" s="9">
         <v>45</v>
       </c>
@@ -7866,8 +8458,11 @@
       <c r="G192" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="193" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H192" s="29">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A193" s="9">
         <v>46</v>
       </c>
@@ -7888,8 +8483,11 @@
       <c r="G193" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="194" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H193" s="29">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A194" s="9">
         <v>46</v>
       </c>
@@ -7912,8 +8510,11 @@
       <c r="G194" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="195" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H194" s="29">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A195" s="9">
         <v>46</v>
       </c>
@@ -7936,8 +8537,11 @@
       <c r="G195" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="196" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H195" s="29">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A196" s="9">
         <v>47</v>
       </c>
@@ -7958,8 +8562,11 @@
       <c r="G196" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="197" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H196" s="29">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A197" s="9">
         <v>47</v>
       </c>
@@ -7982,8 +8589,11 @@
       <c r="G197" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="198" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H197" s="29">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A198" s="9">
         <v>47</v>
       </c>
@@ -8006,8 +8616,11 @@
       <c r="G198" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="199" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H198" s="29">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A199" s="9">
         <v>47</v>
       </c>
@@ -8030,8 +8643,11 @@
       <c r="G199" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="200" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H199" s="29">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A200" s="9">
         <v>47</v>
       </c>
@@ -8054,8 +8670,11 @@
       <c r="G200" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="201" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H200" s="29">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A201" s="9">
         <v>48</v>
       </c>
@@ -8076,8 +8695,11 @@
       <c r="G201" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="202" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H201" s="29">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A202" s="9">
         <v>48</v>
       </c>
@@ -8100,8 +8722,11 @@
       <c r="G202" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="203" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H202" s="29">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A203" s="9">
         <v>48</v>
       </c>
@@ -8124,8 +8749,11 @@
       <c r="G203" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="204" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H203" s="29">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A204" s="9">
         <v>48</v>
       </c>
@@ -8148,8 +8776,11 @@
       <c r="G204" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="205" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H204" s="29">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A205" s="9">
         <v>48</v>
       </c>
@@ -8172,8 +8803,11 @@
       <c r="G205" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="206" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H205" s="29">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A206" s="9">
         <v>48</v>
       </c>
@@ -8196,8 +8830,11 @@
       <c r="G206" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="207" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H206" s="29">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A207" s="9">
         <v>49</v>
       </c>
@@ -8218,8 +8855,11 @@
       <c r="G207" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="208" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H207" s="29">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A208" s="9">
         <v>49</v>
       </c>
@@ -8242,8 +8882,11 @@
       <c r="G208" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="209" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H208" s="29">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A209" s="9">
         <v>50</v>
       </c>
@@ -8264,8 +8907,11 @@
       <c r="G209" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="210" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H209" s="29">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A210" s="9">
         <v>50</v>
       </c>
@@ -8288,8 +8934,11 @@
       <c r="G210" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="211" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H210" s="29">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A211" s="9">
         <v>50</v>
       </c>
@@ -8312,8 +8961,11 @@
       <c r="G211" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="212" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H211" s="29">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A212" s="9">
         <v>50</v>
       </c>
@@ -8336,8 +8988,11 @@
       <c r="G212" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="213" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H212" s="29">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A213" s="9">
         <v>50</v>
       </c>
@@ -8360,8 +9015,11 @@
       <c r="G213" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="214" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H213" s="29">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A214" s="9">
         <v>50</v>
       </c>
@@ -8384,8 +9042,11 @@
       <c r="G214" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="215" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H214" s="29">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A215" s="9">
         <v>50</v>
       </c>
@@ -8408,8 +9069,11 @@
       <c r="G215" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="216" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H215" s="29">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A216" s="9">
         <v>50</v>
       </c>
@@ -8432,8 +9096,11 @@
       <c r="G216" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="217" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H216" s="29">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A217" s="9">
         <v>50</v>
       </c>
@@ -8456,8 +9123,11 @@
       <c r="G217" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="218" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H217" s="29">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A218" s="9">
         <v>50</v>
       </c>
@@ -8480,8 +9150,11 @@
       <c r="G218" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="219" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H218" s="29">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A219" s="9">
         <v>51</v>
       </c>
@@ -8502,8 +9175,11 @@
       <c r="G219" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="220" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H219" s="29">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A220" s="9">
         <v>51</v>
       </c>
@@ -8526,8 +9202,11 @@
       <c r="G220" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="221" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H220" s="29">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A221" s="9">
         <v>51</v>
       </c>
@@ -8550,8 +9229,11 @@
       <c r="G221" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="222" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H221" s="29">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A222" s="9">
         <v>52</v>
       </c>
@@ -8572,8 +9254,11 @@
       <c r="G222" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="223" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H222" s="29">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A223" s="9">
         <v>52</v>
       </c>
@@ -8596,8 +9281,11 @@
       <c r="G223" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="224" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H223" s="29">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A224" s="9">
         <v>52</v>
       </c>
@@ -8620,8 +9308,11 @@
       <c r="G224" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="225" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H224" s="29">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A225" s="9">
         <v>52</v>
       </c>
@@ -8644,8 +9335,11 @@
       <c r="G225" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="226" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H225" s="29">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A226" s="9">
         <v>52</v>
       </c>
@@ -8668,8 +9362,11 @@
       <c r="G226" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="227" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H226" s="29">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A227" s="9">
         <v>52</v>
       </c>
@@ -8692,8 +9389,11 @@
       <c r="G227" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="228" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H227" s="29">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A228" s="9">
         <v>52</v>
       </c>
@@ -8716,8 +9416,11 @@
       <c r="G228" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="229" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H228" s="29">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A229" s="9">
         <v>52</v>
       </c>
@@ -8740,8 +9443,11 @@
       <c r="G229" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="230" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H229" s="29">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A230" s="9">
         <v>52</v>
       </c>
@@ -8764,8 +9470,11 @@
       <c r="G230" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="231" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H230" s="29">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A231" s="9">
         <v>53</v>
       </c>
@@ -8786,8 +9495,11 @@
       <c r="G231" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="232" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H231" s="29">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A232" s="9">
         <v>53</v>
       </c>
@@ -8810,8 +9522,11 @@
       <c r="G232" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="233" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H232" s="29">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A233" s="9">
         <v>53</v>
       </c>
@@ -8834,8 +9549,11 @@
       <c r="G233" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="234" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H233" s="29">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A234" s="9">
         <v>53</v>
       </c>
@@ -8858,8 +9576,11 @@
       <c r="G234" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="235" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H234" s="29">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A235" s="9">
         <v>54</v>
       </c>
@@ -8880,8 +9601,11 @@
       <c r="G235" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="236" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H235" s="29">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A236" s="9">
         <v>54</v>
       </c>
@@ -8904,8 +9628,11 @@
       <c r="G236" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="237" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H236" s="29">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A237" s="9">
         <v>54</v>
       </c>
@@ -8928,8 +9655,11 @@
       <c r="G237" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="238" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H237" s="29">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A238" s="9">
         <v>54</v>
       </c>
@@ -8952,8 +9682,11 @@
       <c r="G238" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="239" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H238" s="29">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A239" s="9">
         <v>55</v>
       </c>
@@ -8974,8 +9707,11 @@
       <c r="G239" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="240" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H239" s="29">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A240" s="9">
         <v>55</v>
       </c>
@@ -8998,8 +9734,11 @@
       <c r="G240" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="241" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H240" s="29">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A241" s="9">
         <v>56</v>
       </c>
@@ -9020,8 +9759,11 @@
       <c r="G241" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="242" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H241" s="29">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A242" s="9">
         <v>56</v>
       </c>
@@ -9044,8 +9786,11 @@
       <c r="G242" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="243" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H242" s="29">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A243" s="9">
         <v>56</v>
       </c>
@@ -9068,8 +9813,11 @@
       <c r="G243" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="244" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H243" s="29">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A244" s="9">
         <v>57</v>
       </c>
@@ -9090,8 +9838,11 @@
       <c r="G244" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="245" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H244" s="29">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A245" s="9">
         <v>57</v>
       </c>
@@ -9114,8 +9865,11 @@
       <c r="G245" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="246" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H245" s="29">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A246" s="9">
         <v>57</v>
       </c>
@@ -9138,8 +9892,11 @@
       <c r="G246" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="247" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H246" s="29">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A247" s="9">
         <v>57</v>
       </c>
@@ -9162,8 +9919,11 @@
       <c r="G247" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="248" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H247" s="29">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A248" s="9">
         <v>57</v>
       </c>
@@ -9186,8 +9946,11 @@
       <c r="G248" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="249" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H248" s="29">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A249" s="9">
         <v>57</v>
       </c>
@@ -9210,8 +9973,11 @@
       <c r="G249" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="250" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H249" s="29">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A250" s="9">
         <v>57</v>
       </c>
@@ -9234,8 +10000,11 @@
       <c r="G250" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="251" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H250" s="29">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A251" s="9">
         <v>57</v>
       </c>
@@ -9258,8 +10027,11 @@
       <c r="G251" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="252" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H251" s="29">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A252" s="9">
         <v>57</v>
       </c>
@@ -9282,8 +10054,11 @@
       <c r="G252" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="253" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H252" s="29">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A253" s="9">
         <v>58</v>
       </c>
@@ -9304,8 +10079,11 @@
       <c r="G253" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="254" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H253" s="29">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A254" s="9">
         <v>58</v>
       </c>
@@ -9328,8 +10106,11 @@
       <c r="G254" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="255" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H254" s="29">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A255" s="9">
         <v>58</v>
       </c>
@@ -9352,8 +10133,11 @@
       <c r="G255" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="256" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H255" s="29">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A256" s="9">
         <v>58</v>
       </c>
@@ -9376,8 +10160,11 @@
       <c r="G256" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="257" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H256" s="29">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A257" s="9">
         <v>58</v>
       </c>
@@ -9400,8 +10187,11 @@
       <c r="G257" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="258" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H257" s="29">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A258" s="9">
         <v>58</v>
       </c>
@@ -9424,8 +10214,11 @@
       <c r="G258" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="259" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H258" s="29">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A259" s="9">
         <v>58</v>
       </c>
@@ -9448,8 +10241,11 @@
       <c r="G259" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="260" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H259" s="29">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A260" s="9">
         <v>251</v>
       </c>
@@ -9467,8 +10263,11 @@
         <v>361</v>
       </c>
       <c r="G260" s="4"/>
-    </row>
-    <row r="261" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H260" s="29">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A261" s="9">
         <v>252</v>
       </c>
@@ -9488,8 +10287,11 @@
         <v>363</v>
       </c>
       <c r="G261" s="4"/>
-    </row>
-    <row r="262" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H261" s="29">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A262" s="39">
         <v>70</v>
       </c>
@@ -9507,8 +10309,11 @@
         <v>362</v>
       </c>
       <c r="G262" s="4"/>
-    </row>
-    <row r="263" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H262" s="29">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A263" s="9">
         <v>70</v>
       </c>
@@ -9528,8 +10333,11 @@
         <v>364</v>
       </c>
       <c r="G263" s="4"/>
-    </row>
-    <row r="264" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H263" s="29">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A264" s="9">
         <v>70</v>
       </c>
@@ -9549,8 +10357,11 @@
         <v>365</v>
       </c>
       <c r="G264" s="4"/>
-    </row>
-    <row r="265" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H264" s="29">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A265" s="9">
         <v>70</v>
       </c>
@@ -9570,8 +10381,11 @@
         <v>366</v>
       </c>
       <c r="G265" s="4"/>
-    </row>
-    <row r="266" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H265" s="29">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A266" s="9">
         <v>70</v>
       </c>
@@ -9591,8 +10405,11 @@
         <v>367</v>
       </c>
       <c r="G266" s="4"/>
-    </row>
-    <row r="267" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H266" s="29">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A267" s="9">
         <v>70</v>
       </c>
@@ -9612,8 +10429,11 @@
         <v>368</v>
       </c>
       <c r="G267" s="4"/>
-    </row>
-    <row r="268" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H267" s="29">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A268" s="9">
         <v>70</v>
       </c>
@@ -9633,8 +10453,11 @@
         <v>369</v>
       </c>
       <c r="G268" s="4"/>
-    </row>
-    <row r="269" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H268" s="29">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A269" s="9">
         <v>70</v>
       </c>
@@ -9654,8 +10477,11 @@
         <v>370</v>
       </c>
       <c r="G269" s="4"/>
-    </row>
-    <row r="270" spans="1:7" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H269" s="29">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A270" s="9">
         <v>70</v>
       </c>
@@ -9675,9 +10501,12 @@
         <v>371</v>
       </c>
       <c r="G270" s="4"/>
-    </row>
-    <row r="271" spans="1:7" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A271" s="54">
+      <c r="H270" s="29">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A271" s="69">
         <v>71</v>
       </c>
       <c r="B271" s="34" t="s">
@@ -9693,9 +10522,12 @@
       <c r="F271" s="23" t="s">
         <v>305</v>
       </c>
-    </row>
-    <row r="272" spans="1:7" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A272" s="55"/>
+      <c r="H271" s="29">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="272" spans="1:8" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A272" s="71"/>
       <c r="B272" s="13" t="s">
         <v>306</v>
       </c>
@@ -9711,9 +10543,12 @@
       <c r="F272" s="11" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="273" spans="1:6" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A273" s="55"/>
+      <c r="H272" s="29">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A273" s="71"/>
       <c r="B273" s="13" t="s">
         <v>308</v>
       </c>
@@ -9729,9 +10564,12 @@
       <c r="F273" s="11" t="s">
         <v>309</v>
       </c>
-    </row>
-    <row r="274" spans="1:6" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A274" s="55"/>
+      <c r="H273" s="29">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A274" s="71"/>
       <c r="B274" s="13" t="s">
         <v>310</v>
       </c>
@@ -9747,9 +10585,12 @@
       <c r="F274" s="11" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="275" spans="1:6" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A275" s="56"/>
+      <c r="H274" s="29">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="275" spans="1:8" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A275" s="72"/>
       <c r="B275" s="13" t="s">
         <v>312</v>
       </c>
@@ -9765,9 +10606,12 @@
       <c r="F275" s="11" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="276" spans="1:6" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A276" s="54">
+      <c r="H275" s="29">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="276" spans="1:8" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A276" s="69">
         <v>72</v>
       </c>
       <c r="B276" s="34" t="s">
@@ -9783,9 +10627,12 @@
       <c r="F276" s="23" t="s">
         <v>315</v>
       </c>
-    </row>
-    <row r="277" spans="1:6" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A277" s="55"/>
+      <c r="H276" s="29">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="277" spans="1:8" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A277" s="71"/>
       <c r="B277" s="13" t="s">
         <v>316</v>
       </c>
@@ -9801,9 +10648,12 @@
       <c r="F277" s="11" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="278" spans="1:6" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A278" s="55"/>
+      <c r="H277" s="29">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="278" spans="1:8" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A278" s="71"/>
       <c r="B278" s="13" t="s">
         <v>318</v>
       </c>
@@ -9819,9 +10669,12 @@
       <c r="F278" s="11" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="279" spans="1:6" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A279" s="56"/>
+      <c r="H278" s="29">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="279" spans="1:8" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A279" s="72"/>
       <c r="B279" s="13" t="s">
         <v>320</v>
       </c>
@@ -9837,9 +10690,12 @@
       <c r="F279" s="11" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="280" spans="1:6" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A280" s="54">
+      <c r="H279" s="29">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="280" spans="1:8" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A280" s="69">
         <v>73</v>
       </c>
       <c r="B280" s="34" t="s">
@@ -9855,9 +10711,12 @@
       <c r="F280" s="23" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="281" spans="1:6" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A281" s="55"/>
+      <c r="H280" s="29">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A281" s="71"/>
       <c r="B281" s="13" t="s">
         <v>324</v>
       </c>
@@ -9873,9 +10732,12 @@
       <c r="F281" s="11" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="282" spans="1:6" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A282" s="55"/>
+      <c r="H281" s="29">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A282" s="71"/>
       <c r="B282" s="13" t="s">
         <v>326</v>
       </c>
@@ -9891,9 +10753,12 @@
       <c r="F282" s="11" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="283" spans="1:6" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A283" s="56"/>
+      <c r="H282" s="29">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="283" spans="1:8" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A283" s="72"/>
       <c r="B283" s="13" t="s">
         <v>328</v>
       </c>
@@ -9909,9 +10774,12 @@
       <c r="F283" s="11" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="284" spans="1:6" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A284" s="54">
+      <c r="H283" s="29">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="284" spans="1:8" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A284" s="69">
         <v>74</v>
       </c>
       <c r="B284" s="34" t="s">
@@ -9927,9 +10795,12 @@
       <c r="F284" s="23" t="s">
         <v>331</v>
       </c>
-    </row>
-    <row r="285" spans="1:6" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A285" s="55"/>
+      <c r="H284" s="29">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="285" spans="1:8" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A285" s="71"/>
       <c r="B285" s="13" t="s">
         <v>332</v>
       </c>
@@ -9945,9 +10816,12 @@
       <c r="F285" s="11" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="286" spans="1:6" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A286" s="56"/>
+      <c r="H285" s="29">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="286" spans="1:8" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A286" s="72"/>
       <c r="B286" s="13" t="s">
         <v>334</v>
       </c>
@@ -9963,9 +10837,12 @@
       <c r="F286" s="11" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="287" spans="1:6" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A287" s="54">
+      <c r="H286" s="29">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="287" spans="1:8" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A287" s="69">
         <v>75</v>
       </c>
       <c r="B287" s="13" t="s">
@@ -9981,9 +10858,12 @@
       <c r="F287" s="11" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="288" spans="1:6" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A288" s="55"/>
+      <c r="H287" s="29">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="288" spans="1:8" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A288" s="71"/>
       <c r="B288" s="13" t="s">
         <v>338</v>
       </c>
@@ -9999,9 +10879,12 @@
       <c r="F288" s="11" t="s">
         <v>339</v>
       </c>
-    </row>
-    <row r="289" spans="1:9" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A289" s="55"/>
+      <c r="H288" s="29">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="289" spans="1:9" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A289" s="71"/>
       <c r="B289" s="13" t="s">
         <v>340</v>
       </c>
@@ -10017,9 +10900,12 @@
       <c r="F289" s="11" t="s">
         <v>341</v>
       </c>
-    </row>
-    <row r="290" spans="1:9" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A290" s="56"/>
+      <c r="H289" s="29">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="290" spans="1:9" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A290" s="72"/>
       <c r="B290" s="13" t="s">
         <v>342</v>
       </c>
@@ -10035,9 +10921,12 @@
       <c r="F290" s="11" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="291" spans="1:9" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A291" s="54">
+      <c r="H290" s="29">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="291" spans="1:9" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A291" s="69">
         <v>76</v>
       </c>
       <c r="B291" s="13" t="s">
@@ -10053,9 +10942,12 @@
       <c r="F291" s="11" t="s">
         <v>348</v>
       </c>
-    </row>
-    <row r="292" spans="1:9" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A292" s="55"/>
+      <c r="H291" s="29">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="292" spans="1:9" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A292" s="71"/>
       <c r="B292" s="13" t="s">
         <v>349</v>
       </c>
@@ -10071,9 +10963,12 @@
       <c r="F292" s="11" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="293" spans="1:9" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A293" s="55"/>
+      <c r="H292" s="29">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="293" spans="1:9" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A293" s="71"/>
       <c r="B293" s="13" t="s">
         <v>351</v>
       </c>
@@ -10089,9 +10984,12 @@
       <c r="F293" s="11" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="294" spans="1:9" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A294" s="56"/>
+      <c r="H293" s="29">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="294" spans="1:9" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A294" s="72"/>
       <c r="B294" s="13" t="s">
         <v>353</v>
       </c>
@@ -10107,9 +11005,12 @@
       <c r="F294" s="11" t="s">
         <v>354</v>
       </c>
-    </row>
-    <row r="295" spans="1:9" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A295" s="54">
+      <c r="H294" s="29">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="295" spans="1:9" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A295" s="69">
         <v>77</v>
       </c>
       <c r="B295" s="34" t="s">
@@ -10125,9 +11026,12 @@
       <c r="F295" s="23" t="s">
         <v>356</v>
       </c>
-    </row>
-    <row r="296" spans="1:9" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A296" s="57"/>
+      <c r="H295" s="29">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="296" spans="1:9" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A296" s="70"/>
       <c r="B296" s="13" t="s">
         <v>357</v>
       </c>
@@ -10143,9 +11047,12 @@
       <c r="F296" s="11" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="297" spans="1:9" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A297" s="57"/>
+      <c r="H296" s="29">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="297" spans="1:9" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A297" s="70"/>
       <c r="B297" s="13" t="s">
         <v>359</v>
       </c>
@@ -10161,21 +11068,24 @@
       <c r="F297" s="11" t="s">
         <v>360</v>
       </c>
+      <c r="H297" s="29">
+        <v>296</v>
+      </c>
     </row>
     <row r="298" spans="1:9" ht="80.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A298" s="58" t="s">
+      <c r="A298" s="73" t="s">
         <v>408</v>
       </c>
-      <c r="B298" s="58"/>
-      <c r="C298" s="58"/>
-      <c r="D298" s="58"/>
-      <c r="E298" s="58"/>
-      <c r="F298" s="58"/>
-      <c r="G298" s="58"/>
-      <c r="H298" s="58"/>
-      <c r="I298" s="58"/>
-    </row>
-    <row r="299" spans="1:9" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B298" s="73"/>
+      <c r="C298" s="73"/>
+      <c r="D298" s="73"/>
+      <c r="E298" s="73"/>
+      <c r="F298" s="73"/>
+      <c r="G298" s="73"/>
+      <c r="H298" s="73"/>
+      <c r="I298" s="73"/>
+    </row>
+    <row r="299" spans="1:9" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A299" s="9">
         <v>78</v>
       </c>
@@ -10199,7 +11109,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="300" spans="1:9" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="300" spans="1:9" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A300" s="9">
         <v>79</v>
       </c>
@@ -10223,7 +11133,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="301" spans="1:9" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="301" spans="1:9" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A301" s="9">
         <v>80</v>
       </c>
@@ -10247,7 +11157,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="302" spans="1:9" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="302" spans="1:9" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A302" s="9">
         <v>81</v>
       </c>
@@ -10271,7 +11181,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="303" spans="1:9" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="303" spans="1:9" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A303" s="9">
         <v>82</v>
       </c>
@@ -10295,7 +11205,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="304" spans="1:9" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="304" spans="1:9" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A304" s="9">
         <v>83</v>
       </c>
@@ -10319,7 +11229,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="305" spans="1:9" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="305" spans="1:9" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A305" s="9">
         <v>84</v>
       </c>
@@ -10343,7 +11253,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="306" spans="1:9" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="306" spans="1:9" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A306" s="51">
         <v>85</v>
       </c>
@@ -10367,7 +11277,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="307" spans="1:9" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="307" spans="1:9" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A307" s="52"/>
       <c r="B307" s="13" t="s">
         <v>381</v>
@@ -10389,7 +11299,7 @@
       </c>
       <c r="I307" s="50"/>
     </row>
-    <row r="308" spans="1:9" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="308" spans="1:9" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A308" s="53"/>
       <c r="B308" s="13" t="s">
         <v>382</v>
@@ -10411,7 +11321,7 @@
       </c>
       <c r="I308" s="50"/>
     </row>
-    <row r="309" spans="1:9" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="309" spans="1:9" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A309" s="51">
         <v>86</v>
       </c>
@@ -10435,7 +11345,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="310" spans="1:9" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="310" spans="1:9" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A310" s="53"/>
       <c r="B310" s="13" t="s">
         <v>385</v>
@@ -10458,32 +11368,32 @@
       <c r="I310" s="50"/>
     </row>
     <row r="311" spans="1:9" ht="78" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A311" s="59" t="s">
+      <c r="A311" s="68" t="s">
         <v>409</v>
       </c>
-      <c r="B311" s="59"/>
-      <c r="C311" s="59"/>
-      <c r="D311" s="59"/>
-      <c r="E311" s="59"/>
-      <c r="F311" s="59"/>
-      <c r="G311" s="59"/>
-      <c r="H311" s="59"/>
-      <c r="I311" s="59"/>
-    </row>
-    <row r="312" spans="1:9" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A312" s="60" t="s">
+      <c r="B311" s="68"/>
+      <c r="C311" s="68"/>
+      <c r="D311" s="68"/>
+      <c r="E311" s="68"/>
+      <c r="F311" s="68"/>
+      <c r="G311" s="68"/>
+      <c r="H311" s="68"/>
+      <c r="I311" s="68"/>
+    </row>
+    <row r="312" spans="1:9" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A312" s="54" t="s">
         <v>410</v>
       </c>
-      <c r="B312" s="61" t="s">
+      <c r="B312" s="55" t="s">
         <v>411</v>
       </c>
-      <c r="C312" s="62" t="s">
+      <c r="C312" s="56" t="s">
         <v>412</v>
       </c>
-      <c r="D312" s="62" t="s">
+      <c r="D312" s="56" t="s">
         <v>413</v>
       </c>
-      <c r="E312" s="63" t="s">
+      <c r="E312" s="57" t="s">
         <v>414</v>
       </c>
       <c r="F312" s="3" t="s">
@@ -10493,1257 +11403,1257 @@
         <v>415</v>
       </c>
     </row>
-    <row r="313" spans="1:9" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A313" s="64">
+    <row r="313" spans="1:9" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A313" s="58">
         <v>87</v>
       </c>
-      <c r="B313" s="65" t="s">
+      <c r="B313" s="59" t="s">
         <v>416</v>
       </c>
-      <c r="C313" s="66">
+      <c r="C313" s="60">
         <v>32321</v>
       </c>
-      <c r="D313" s="67" t="s">
+      <c r="D313" s="61" t="s">
         <v>51</v>
       </c>
-      <c r="E313" s="64">
+      <c r="E313" s="58">
         <v>87</v>
       </c>
-      <c r="F313" s="68" t="s">
+      <c r="F313" s="62" t="s">
         <v>418</v>
       </c>
-      <c r="G313" s="69" t="s">
+      <c r="G313" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="314" spans="1:9" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A314" s="70"/>
-      <c r="B314" s="65" t="s">
+    <row r="314" spans="1:9" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A314" s="64"/>
+      <c r="B314" s="59" t="s">
         <v>419</v>
       </c>
-      <c r="C314" s="66">
+      <c r="C314" s="60">
         <v>18629</v>
       </c>
-      <c r="D314" s="66" t="s">
+      <c r="D314" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="E314" s="66" t="s">
+      <c r="E314" s="60" t="s">
         <v>420</v>
       </c>
-      <c r="F314" s="68" t="s">
+      <c r="F314" s="62" t="s">
         <v>421</v>
       </c>
-      <c r="G314" s="69" t="s">
+      <c r="G314" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="315" spans="1:9" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A315" s="70"/>
-      <c r="B315" s="65" t="s">
+    <row r="315" spans="1:9" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A315" s="64"/>
+      <c r="B315" s="59" t="s">
         <v>422</v>
       </c>
-      <c r="C315" s="66">
+      <c r="C315" s="60">
         <v>21186</v>
       </c>
-      <c r="D315" s="66" t="s">
+      <c r="D315" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="E315" s="66" t="s">
+      <c r="E315" s="60" t="s">
         <v>423</v>
       </c>
-      <c r="F315" s="68" t="s">
+      <c r="F315" s="62" t="s">
         <v>424</v>
       </c>
-      <c r="G315" s="69" t="s">
+      <c r="G315" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="316" spans="1:9" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A316" s="64">
+    <row r="316" spans="1:9" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A316" s="58">
         <v>88</v>
       </c>
-      <c r="B316" s="65" t="s">
+      <c r="B316" s="59" t="s">
         <v>425</v>
       </c>
-      <c r="C316" s="66">
+      <c r="C316" s="60">
         <v>36592</v>
       </c>
-      <c r="D316" s="66" t="s">
+      <c r="D316" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="E316" s="64">
+      <c r="E316" s="58">
         <v>88</v>
       </c>
-      <c r="F316" s="68" t="s">
+      <c r="F316" s="62" t="s">
         <v>426</v>
       </c>
-      <c r="G316" s="69" t="s">
+      <c r="G316" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="317" spans="1:9" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A317" s="70"/>
-      <c r="B317" s="65" t="s">
+    <row r="317" spans="1:9" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A317" s="64"/>
+      <c r="B317" s="59" t="s">
         <v>427</v>
       </c>
-      <c r="C317" s="66">
+      <c r="C317" s="60">
         <v>22282</v>
       </c>
-      <c r="D317" s="66" t="s">
+      <c r="D317" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="E317" s="66" t="s">
+      <c r="E317" s="60" t="s">
         <v>420</v>
       </c>
-      <c r="F317" s="68" t="s">
+      <c r="F317" s="62" t="s">
         <v>428</v>
       </c>
-      <c r="G317" s="69" t="s">
+      <c r="G317" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="318" spans="1:9" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A318" s="70"/>
-      <c r="B318" s="65" t="s">
+    <row r="318" spans="1:9" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A318" s="64"/>
+      <c r="B318" s="59" t="s">
         <v>429</v>
       </c>
-      <c r="C318" s="66">
+      <c r="C318" s="60">
         <v>25820</v>
       </c>
-      <c r="D318" s="66" t="s">
+      <c r="D318" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="E318" s="66" t="s">
+      <c r="E318" s="60" t="s">
         <v>423</v>
       </c>
-      <c r="F318" s="68" t="s">
+      <c r="F318" s="62" t="s">
         <v>430</v>
       </c>
-      <c r="G318" s="69" t="s">
+      <c r="G318" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="319" spans="1:9" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A319" s="70"/>
-      <c r="B319" s="65" t="s">
+    <row r="319" spans="1:9" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A319" s="64"/>
+      <c r="B319" s="59" t="s">
         <v>431</v>
       </c>
-      <c r="C319" s="66">
+      <c r="C319" s="60">
         <v>37465</v>
       </c>
-      <c r="D319" s="66" t="s">
+      <c r="D319" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="E319" s="66" t="s">
+      <c r="E319" s="60" t="s">
         <v>432</v>
       </c>
-      <c r="F319" s="68" t="s">
+      <c r="F319" s="62" t="s">
         <v>433</v>
       </c>
-      <c r="G319" s="69" t="s">
+      <c r="G319" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="320" spans="1:9" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A320" s="70"/>
-      <c r="B320" s="65" t="s">
+    <row r="320" spans="1:9" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A320" s="64"/>
+      <c r="B320" s="59" t="s">
         <v>434</v>
       </c>
-      <c r="C320" s="66">
+      <c r="C320" s="60">
         <v>44984</v>
       </c>
-      <c r="D320" s="66" t="s">
+      <c r="D320" s="60" t="s">
         <v>53</v>
       </c>
-      <c r="E320" s="66" t="s">
+      <c r="E320" s="60" t="s">
         <v>435</v>
       </c>
-      <c r="F320" s="68" t="s">
+      <c r="F320" s="62" t="s">
         <v>436</v>
       </c>
-      <c r="G320" s="69" t="s">
+      <c r="G320" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="321" spans="1:7" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A321" s="70"/>
-      <c r="B321" s="65" t="s">
+    <row r="321" spans="1:7" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A321" s="64"/>
+      <c r="B321" s="59" t="s">
         <v>437</v>
       </c>
-      <c r="C321" s="66">
+      <c r="C321" s="60">
         <v>45547</v>
       </c>
-      <c r="D321" s="66" t="s">
+      <c r="D321" s="60" t="s">
         <v>54</v>
       </c>
-      <c r="E321" s="66" t="s">
+      <c r="E321" s="60" t="s">
         <v>438</v>
       </c>
-      <c r="F321" s="68" t="s">
+      <c r="F321" s="62" t="s">
         <v>439</v>
       </c>
-      <c r="G321" s="69" t="s">
+      <c r="G321" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="322" spans="1:7" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A322" s="70"/>
-      <c r="B322" s="65" t="s">
+    <row r="322" spans="1:7" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A322" s="64"/>
+      <c r="B322" s="59" t="s">
         <v>440</v>
       </c>
-      <c r="C322" s="66">
+      <c r="C322" s="60">
         <v>46030</v>
       </c>
-      <c r="D322" s="66" t="s">
+      <c r="D322" s="60" t="s">
         <v>54</v>
       </c>
-      <c r="E322" s="66" t="s">
+      <c r="E322" s="60" t="s">
         <v>441</v>
       </c>
-      <c r="F322" s="68" t="s">
+      <c r="F322" s="62" t="s">
         <v>442</v>
       </c>
-      <c r="G322" s="69" t="s">
+      <c r="G322" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="323" spans="1:7" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A323" s="64">
+    <row r="323" spans="1:7" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A323" s="58">
         <v>89</v>
       </c>
-      <c r="B323" s="65" t="s">
+      <c r="B323" s="59" t="s">
         <v>443</v>
       </c>
-      <c r="C323" s="66">
+      <c r="C323" s="60">
         <v>37649</v>
       </c>
-      <c r="D323" s="66" t="s">
+      <c r="D323" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="E323" s="64">
+      <c r="E323" s="58">
         <v>89</v>
       </c>
-      <c r="F323" s="71" t="s">
+      <c r="F323" s="65" t="s">
         <v>444</v>
       </c>
-      <c r="G323" s="69" t="s">
+      <c r="G323" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="324" spans="1:7" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A324" s="70"/>
-      <c r="B324" s="65" t="s">
+    <row r="324" spans="1:7" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A324" s="64"/>
+      <c r="B324" s="59" t="s">
         <v>445</v>
       </c>
-      <c r="C324" s="66">
+      <c r="C324" s="60">
         <v>23794</v>
       </c>
-      <c r="D324" s="66" t="s">
+      <c r="D324" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="E324" s="66" t="s">
+      <c r="E324" s="60" t="s">
         <v>420</v>
       </c>
-      <c r="F324" s="71" t="s">
+      <c r="F324" s="65" t="s">
         <v>446</v>
       </c>
-      <c r="G324" s="69" t="s">
+      <c r="G324" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="325" spans="1:7" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A325" s="64">
+    <row r="325" spans="1:7" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A325" s="58">
         <v>28</v>
       </c>
-      <c r="B325" s="65" t="s">
+      <c r="B325" s="59" t="s">
         <v>447</v>
       </c>
-      <c r="C325" s="66">
+      <c r="C325" s="60">
         <v>46029</v>
       </c>
-      <c r="D325" s="66" t="s">
+      <c r="D325" s="60" t="s">
         <v>53</v>
       </c>
-      <c r="E325" s="64">
+      <c r="E325" s="58">
         <v>28</v>
       </c>
-      <c r="F325" s="71" t="s">
+      <c r="F325" s="65" t="s">
         <v>448</v>
       </c>
-      <c r="G325" s="69" t="s">
+      <c r="G325" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="326" spans="1:7" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A326" s="64">
+    <row r="326" spans="1:7" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A326" s="58">
         <v>90</v>
       </c>
-      <c r="B326" s="65" t="s">
+      <c r="B326" s="59" t="s">
         <v>449</v>
       </c>
-      <c r="C326" s="66">
+      <c r="C326" s="60">
         <v>27368</v>
       </c>
-      <c r="D326" s="66" t="s">
+      <c r="D326" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="E326" s="64">
+      <c r="E326" s="58">
         <v>90</v>
       </c>
-      <c r="F326" s="71" t="s">
+      <c r="F326" s="65" t="s">
         <v>450</v>
       </c>
-      <c r="G326" s="69" t="s">
+      <c r="G326" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="327" spans="1:7" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A327" s="70"/>
-      <c r="B327" s="65" t="s">
+    <row r="327" spans="1:7" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A327" s="64"/>
+      <c r="B327" s="59" t="s">
         <v>451</v>
       </c>
-      <c r="C327" s="66">
+      <c r="C327" s="60">
         <v>30193</v>
       </c>
-      <c r="D327" s="66" t="s">
+      <c r="D327" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="E327" s="66" t="s">
+      <c r="E327" s="60" t="s">
         <v>423</v>
       </c>
-      <c r="F327" s="71" t="s">
+      <c r="F327" s="65" t="s">
         <v>452</v>
       </c>
-      <c r="G327" s="69" t="s">
+      <c r="G327" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="328" spans="1:7" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A328" s="70"/>
-      <c r="B328" s="65" t="s">
+    <row r="328" spans="1:7" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A328" s="64"/>
+      <c r="B328" s="59" t="s">
         <v>453</v>
       </c>
-      <c r="C328" s="66">
+      <c r="C328" s="60">
         <v>42635</v>
       </c>
-      <c r="D328" s="66" t="s">
+      <c r="D328" s="60" t="s">
         <v>54</v>
       </c>
-      <c r="E328" s="66"/>
-      <c r="F328" s="71" t="s">
+      <c r="E328" s="60"/>
+      <c r="F328" s="65" t="s">
         <v>454</v>
       </c>
-      <c r="G328" s="69" t="s">
+      <c r="G328" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="329" spans="1:7" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A329" s="70"/>
-      <c r="B329" s="65" t="s">
+    <row r="329" spans="1:7" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A329" s="64"/>
+      <c r="B329" s="59" t="s">
         <v>455</v>
       </c>
-      <c r="C329" s="66">
+      <c r="C329" s="60">
         <v>43059</v>
       </c>
-      <c r="D329" s="66" t="s">
+      <c r="D329" s="60" t="s">
         <v>54</v>
       </c>
-      <c r="E329" s="66" t="s">
+      <c r="E329" s="60" t="s">
         <v>432</v>
       </c>
-      <c r="F329" s="71" t="s">
+      <c r="F329" s="65" t="s">
         <v>456</v>
       </c>
-      <c r="G329" s="69" t="s">
+      <c r="G329" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="330" spans="1:7" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A330" s="70"/>
-      <c r="B330" s="65" t="s">
+    <row r="330" spans="1:7" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A330" s="64"/>
+      <c r="B330" s="59" t="s">
         <v>457</v>
       </c>
-      <c r="C330" s="66">
+      <c r="C330" s="60">
         <v>43727</v>
       </c>
-      <c r="D330" s="66" t="s">
+      <c r="D330" s="60" t="s">
         <v>53</v>
       </c>
-      <c r="E330" s="66" t="s">
+      <c r="E330" s="60" t="s">
         <v>441</v>
       </c>
-      <c r="F330" s="71" t="s">
+      <c r="F330" s="65" t="s">
         <v>458</v>
       </c>
-      <c r="G330" s="69" t="s">
+      <c r="G330" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="331" spans="1:7" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A331" s="64">
+    <row r="331" spans="1:7" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A331" s="58">
         <v>91</v>
       </c>
-      <c r="B331" s="65" t="s">
+      <c r="B331" s="59" t="s">
         <v>459</v>
       </c>
-      <c r="C331" s="66">
+      <c r="C331" s="60">
         <v>22686</v>
       </c>
-      <c r="D331" s="66" t="s">
+      <c r="D331" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="E331" s="64">
+      <c r="E331" s="58">
         <v>91</v>
       </c>
-      <c r="F331" s="71" t="s">
+      <c r="F331" s="65" t="s">
         <v>460</v>
       </c>
-      <c r="G331" s="69" t="s">
+      <c r="G331" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="332" spans="1:7" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A332" s="70"/>
-      <c r="B332" s="65" t="s">
+    <row r="332" spans="1:7" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A332" s="64"/>
+      <c r="B332" s="59" t="s">
         <v>461</v>
       </c>
-      <c r="C332" s="66">
+      <c r="C332" s="60">
         <v>22566</v>
       </c>
-      <c r="D332" s="66" t="s">
+      <c r="D332" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="E332" s="66" t="s">
+      <c r="E332" s="60" t="s">
         <v>420</v>
       </c>
-      <c r="F332" s="71" t="s">
+      <c r="F332" s="65" t="s">
         <v>462</v>
       </c>
-      <c r="G332" s="69" t="s">
+      <c r="G332" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="333" spans="1:7" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A333" s="70"/>
-      <c r="B333" s="65" t="s">
+    <row r="333" spans="1:7" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A333" s="64"/>
+      <c r="B333" s="59" t="s">
         <v>463</v>
       </c>
-      <c r="C333" s="66">
+      <c r="C333" s="60">
         <v>36410</v>
       </c>
-      <c r="D333" s="66" t="s">
+      <c r="D333" s="60" t="s">
         <v>53</v>
       </c>
-      <c r="E333" s="66" t="s">
+      <c r="E333" s="60" t="s">
         <v>423</v>
       </c>
-      <c r="F333" s="71" t="s">
+      <c r="F333" s="65" t="s">
         <v>464</v>
       </c>
-      <c r="G333" s="69" t="s">
+      <c r="G333" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="334" spans="1:7" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A334" s="64">
+    <row r="334" spans="1:7" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A334" s="58">
         <v>92</v>
       </c>
-      <c r="B334" s="65" t="s">
+      <c r="B334" s="59" t="s">
         <v>465</v>
       </c>
-      <c r="C334" s="66">
+      <c r="C334" s="60">
         <v>38895</v>
       </c>
-      <c r="D334" s="66" t="s">
+      <c r="D334" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="E334" s="64">
+      <c r="E334" s="58">
         <v>92</v>
       </c>
-      <c r="F334" s="71" t="s">
+      <c r="F334" s="65" t="s">
         <v>466</v>
       </c>
-      <c r="G334" s="69" t="s">
+      <c r="G334" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="335" spans="1:7" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A335" s="70"/>
-      <c r="B335" s="65" t="s">
+    <row r="335" spans="1:7" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A335" s="64"/>
+      <c r="B335" s="59" t="s">
         <v>467</v>
       </c>
-      <c r="C335" s="66">
+      <c r="C335" s="60">
         <v>26729</v>
       </c>
-      <c r="D335" s="66" t="s">
+      <c r="D335" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="E335" s="66" t="s">
+      <c r="E335" s="60" t="s">
         <v>420</v>
       </c>
-      <c r="F335" s="71" t="s">
+      <c r="F335" s="65" t="s">
         <v>468</v>
       </c>
-      <c r="G335" s="69" t="s">
+      <c r="G335" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="336" spans="1:7" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A336" s="70"/>
-      <c r="B336" s="65" t="s">
+    <row r="336" spans="1:7" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A336" s="64"/>
+      <c r="B336" s="59" t="s">
         <v>469</v>
       </c>
-      <c r="C336" s="66">
+      <c r="C336" s="60">
         <v>26034</v>
       </c>
-      <c r="D336" s="66" t="s">
+      <c r="D336" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="E336" s="66" t="s">
+      <c r="E336" s="60" t="s">
         <v>423</v>
       </c>
-      <c r="F336" s="71" t="s">
+      <c r="F336" s="65" t="s">
         <v>470</v>
       </c>
-      <c r="G336" s="69" t="s">
+      <c r="G336" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="337" spans="1:7" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A337" s="64">
+    <row r="337" spans="1:7" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A337" s="58">
         <v>93</v>
       </c>
-      <c r="B337" s="65" t="s">
+      <c r="B337" s="59" t="s">
         <v>471</v>
       </c>
-      <c r="C337" s="66">
+      <c r="C337" s="60">
         <v>37838</v>
       </c>
-      <c r="D337" s="66" t="s">
+      <c r="D337" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="E337" s="64">
+      <c r="E337" s="58">
         <v>93</v>
       </c>
-      <c r="F337" s="71" t="s">
+      <c r="F337" s="65" t="s">
         <v>472</v>
       </c>
-      <c r="G337" s="69" t="s">
+      <c r="G337" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="338" spans="1:7" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A338" s="70"/>
-      <c r="B338" s="65" t="s">
+    <row r="338" spans="1:7" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A338" s="64"/>
+      <c r="B338" s="59" t="s">
         <v>473</v>
       </c>
-      <c r="C338" s="66">
+      <c r="C338" s="60">
         <v>28152</v>
       </c>
-      <c r="D338" s="66" t="s">
+      <c r="D338" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="E338" s="66" t="s">
+      <c r="E338" s="60" t="s">
         <v>420</v>
       </c>
-      <c r="F338" s="71" t="s">
+      <c r="F338" s="65" t="s">
         <v>474</v>
       </c>
-      <c r="G338" s="69" t="s">
+      <c r="G338" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="339" spans="1:7" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A339" s="70"/>
-      <c r="B339" s="65" t="s">
+    <row r="339" spans="1:7" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A339" s="64"/>
+      <c r="B339" s="59" t="s">
         <v>475</v>
       </c>
-      <c r="C339" s="66">
+      <c r="C339" s="60">
         <v>29243</v>
       </c>
-      <c r="D339" s="66" t="s">
+      <c r="D339" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="E339" s="66" t="s">
+      <c r="E339" s="60" t="s">
         <v>423</v>
       </c>
-      <c r="F339" s="71" t="s">
+      <c r="F339" s="65" t="s">
         <v>476</v>
       </c>
-      <c r="G339" s="69" t="s">
+      <c r="G339" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="340" spans="1:7" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A340" s="64">
+    <row r="340" spans="1:7" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A340" s="58">
         <v>94</v>
       </c>
-      <c r="B340" s="65" t="s">
+      <c r="B340" s="59" t="s">
         <v>477</v>
       </c>
-      <c r="C340" s="65">
+      <c r="C340" s="59">
         <v>36126</v>
       </c>
-      <c r="D340" s="65" t="s">
+      <c r="D340" s="59" t="s">
         <v>37</v>
       </c>
-      <c r="E340" s="64">
+      <c r="E340" s="58">
         <v>94</v>
       </c>
-      <c r="F340" s="72" t="s">
+      <c r="F340" s="66" t="s">
         <v>479</v>
       </c>
-      <c r="G340" s="69" t="s">
+      <c r="G340" s="63" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="341" spans="1:7" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A341" s="70"/>
-      <c r="B341" s="65" t="s">
+    <row r="341" spans="1:7" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A341" s="64"/>
+      <c r="B341" s="59" t="s">
         <v>480</v>
       </c>
-      <c r="C341" s="66">
+      <c r="C341" s="60">
         <v>25552</v>
       </c>
-      <c r="D341" s="66" t="s">
+      <c r="D341" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="E341" s="66" t="s">
+      <c r="E341" s="60" t="s">
         <v>420</v>
       </c>
-      <c r="F341" s="72" t="s">
+      <c r="F341" s="66" t="s">
         <v>481</v>
       </c>
-      <c r="G341" s="69" t="s">
+      <c r="G341" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="342" spans="1:7" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A342" s="70"/>
-      <c r="B342" s="65" t="s">
+    <row r="342" spans="1:7" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A342" s="64"/>
+      <c r="B342" s="59" t="s">
         <v>482</v>
       </c>
-      <c r="C342" s="66">
+      <c r="C342" s="60">
         <v>27156</v>
       </c>
-      <c r="D342" s="66" t="s">
+      <c r="D342" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="E342" s="66" t="s">
+      <c r="E342" s="60" t="s">
         <v>423</v>
       </c>
-      <c r="F342" s="72" t="s">
+      <c r="F342" s="66" t="s">
         <v>483</v>
       </c>
-      <c r="G342" s="69" t="s">
+      <c r="G342" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="343" spans="1:7" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A343" s="64">
+    <row r="343" spans="1:7" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A343" s="58">
         <v>95</v>
       </c>
-      <c r="B343" s="65" t="s">
+      <c r="B343" s="59" t="s">
         <v>484</v>
       </c>
-      <c r="C343" s="66">
+      <c r="C343" s="60">
         <v>37897</v>
       </c>
-      <c r="D343" s="66" t="s">
+      <c r="D343" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="E343" s="64">
+      <c r="E343" s="58">
         <v>95</v>
       </c>
-      <c r="F343" s="71" t="s">
+      <c r="F343" s="65" t="s">
         <v>485</v>
       </c>
-      <c r="G343" s="69" t="s">
+      <c r="G343" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="344" spans="1:7" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A344" s="70"/>
-      <c r="B344" s="65" t="s">
+    <row r="344" spans="1:7" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A344" s="64"/>
+      <c r="B344" s="59" t="s">
         <v>486</v>
       </c>
-      <c r="C344" s="66">
+      <c r="C344" s="60">
         <v>23881</v>
       </c>
-      <c r="D344" s="66" t="s">
+      <c r="D344" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="E344" s="66" t="s">
+      <c r="E344" s="60" t="s">
         <v>420</v>
       </c>
-      <c r="F344" s="71" t="s">
+      <c r="F344" s="65" t="s">
         <v>487</v>
       </c>
-      <c r="G344" s="69" t="s">
+      <c r="G344" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="345" spans="1:7" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A345" s="70"/>
-      <c r="B345" s="65" t="s">
+    <row r="345" spans="1:7" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A345" s="64"/>
+      <c r="B345" s="59" t="s">
         <v>488</v>
       </c>
-      <c r="C345" s="66">
+      <c r="C345" s="60">
         <v>25570</v>
       </c>
-      <c r="D345" s="66" t="s">
+      <c r="D345" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="E345" s="66" t="s">
+      <c r="E345" s="60" t="s">
         <v>423</v>
       </c>
-      <c r="F345" s="71" t="s">
+      <c r="F345" s="65" t="s">
         <v>489</v>
       </c>
-      <c r="G345" s="69" t="s">
+      <c r="G345" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="346" spans="1:7" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A346" s="64">
+    <row r="346" spans="1:7" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A346" s="58">
         <v>96</v>
       </c>
-      <c r="B346" s="65" t="s">
+      <c r="B346" s="59" t="s">
         <v>490</v>
       </c>
-      <c r="C346" s="65">
+      <c r="C346" s="59">
         <v>28216</v>
       </c>
-      <c r="D346" s="65" t="s">
+      <c r="D346" s="59" t="s">
         <v>51</v>
       </c>
-      <c r="E346" s="64">
+      <c r="E346" s="58">
         <v>96</v>
       </c>
-      <c r="F346" s="71" t="s">
+      <c r="F346" s="65" t="s">
         <v>491</v>
       </c>
-      <c r="G346" s="69" t="s">
+      <c r="G346" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="347" spans="1:7" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A347" s="70"/>
-      <c r="B347" s="65" t="s">
+    <row r="347" spans="1:7" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A347" s="64"/>
+      <c r="B347" s="59" t="s">
         <v>492</v>
       </c>
-      <c r="C347" s="66">
+      <c r="C347" s="60">
         <v>31891</v>
       </c>
-      <c r="D347" s="66" t="s">
+      <c r="D347" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="E347" s="66" t="s">
+      <c r="E347" s="60" t="s">
         <v>420</v>
       </c>
-      <c r="F347" s="71" t="s">
+      <c r="F347" s="65" t="s">
         <v>493</v>
       </c>
-      <c r="G347" s="69" t="s">
+      <c r="G347" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="348" spans="1:7" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A348" s="70"/>
-      <c r="B348" s="65" t="s">
+    <row r="348" spans="1:7" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A348" s="64"/>
+      <c r="B348" s="59" t="s">
         <v>494</v>
       </c>
-      <c r="C348" s="66">
+      <c r="C348" s="60">
         <v>42432</v>
       </c>
-      <c r="D348" s="66" t="s">
+      <c r="D348" s="60" t="s">
         <v>53</v>
       </c>
-      <c r="E348" s="66" t="s">
+      <c r="E348" s="60" t="s">
         <v>423</v>
       </c>
-      <c r="F348" s="71" t="s">
+      <c r="F348" s="65" t="s">
         <v>495</v>
       </c>
-      <c r="G348" s="69" t="s">
+      <c r="G348" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="349" spans="1:7" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A349" s="70"/>
-      <c r="B349" s="65" t="s">
+    <row r="349" spans="1:7" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A349" s="64"/>
+      <c r="B349" s="59" t="s">
         <v>496</v>
       </c>
-      <c r="C349" s="66">
+      <c r="C349" s="60">
         <v>42923</v>
       </c>
-      <c r="D349" s="66" t="s">
+      <c r="D349" s="60" t="s">
         <v>54</v>
       </c>
-      <c r="E349" s="66" t="s">
+      <c r="E349" s="60" t="s">
         <v>432</v>
       </c>
-      <c r="F349" s="71" t="s">
+      <c r="F349" s="65" t="s">
         <v>497</v>
       </c>
-      <c r="G349" s="69" t="s">
+      <c r="G349" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="350" spans="1:7" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A350" s="70"/>
-      <c r="B350" s="65" t="s">
+    <row r="350" spans="1:7" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A350" s="64"/>
+      <c r="B350" s="59" t="s">
         <v>498</v>
       </c>
-      <c r="C350" s="66" t="s">
+      <c r="C350" s="60" t="s">
         <v>499</v>
       </c>
-      <c r="D350" s="66" t="s">
+      <c r="D350" s="60" t="s">
         <v>54</v>
       </c>
-      <c r="E350" s="66" t="s">
+      <c r="E350" s="60" t="s">
         <v>435</v>
       </c>
-      <c r="F350" s="71" t="s">
+      <c r="F350" s="65" t="s">
         <v>500</v>
       </c>
-      <c r="G350" s="69" t="s">
+      <c r="G350" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="351" spans="1:7" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A351" s="64">
+    <row r="351" spans="1:7" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A351" s="58">
         <v>97</v>
       </c>
-      <c r="B351" s="65" t="s">
+      <c r="B351" s="59" t="s">
         <v>501</v>
       </c>
-      <c r="C351" s="66">
+      <c r="C351" s="60">
         <v>28004</v>
       </c>
-      <c r="D351" s="66" t="s">
+      <c r="D351" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="E351" s="64">
+      <c r="E351" s="58">
         <v>97</v>
       </c>
-      <c r="F351" s="71" t="s">
+      <c r="F351" s="65" t="s">
         <v>502</v>
       </c>
-      <c r="G351" s="69" t="s">
+      <c r="G351" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="352" spans="1:7" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A352" s="70"/>
-      <c r="B352" s="65" t="s">
+    <row r="352" spans="1:7" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A352" s="64"/>
+      <c r="B352" s="59" t="s">
         <v>503</v>
       </c>
-      <c r="C352" s="66">
+      <c r="C352" s="60">
         <v>18501</v>
       </c>
-      <c r="D352" s="66" t="s">
+      <c r="D352" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="E352" s="66" t="s">
+      <c r="E352" s="60" t="s">
         <v>420</v>
       </c>
-      <c r="F352" s="71" t="s">
+      <c r="F352" s="65" t="s">
         <v>504</v>
       </c>
-      <c r="G352" s="69" t="s">
+      <c r="G352" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="353" spans="1:7" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A353" s="70"/>
-      <c r="B353" s="65" t="s">
+    <row r="353" spans="1:7" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A353" s="64"/>
+      <c r="B353" s="59" t="s">
         <v>505</v>
       </c>
-      <c r="C353" s="66">
+      <c r="C353" s="60">
         <v>32686</v>
       </c>
-      <c r="D353" s="66" t="s">
+      <c r="D353" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="E353" s="66" t="s">
+      <c r="E353" s="60" t="s">
         <v>423</v>
       </c>
-      <c r="F353" s="71" t="s">
+      <c r="F353" s="65" t="s">
         <v>506</v>
       </c>
-      <c r="G353" s="69" t="s">
+      <c r="G353" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="354" spans="1:7" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A354" s="70"/>
-      <c r="B354" s="65" t="s">
+    <row r="354" spans="1:7" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A354" s="64"/>
+      <c r="B354" s="59" t="s">
         <v>507</v>
       </c>
-      <c r="C354" s="66">
+      <c r="C354" s="60">
         <v>40765</v>
       </c>
-      <c r="D354" s="66" t="s">
+      <c r="D354" s="60" t="s">
         <v>54</v>
       </c>
-      <c r="E354" s="66" t="s">
+      <c r="E354" s="60" t="s">
         <v>432</v>
       </c>
-      <c r="F354" s="71" t="s">
+      <c r="F354" s="65" t="s">
         <v>508</v>
       </c>
-      <c r="G354" s="69" t="s">
+      <c r="G354" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="355" spans="1:7" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A355" s="70"/>
-      <c r="B355" s="65" t="s">
+    <row r="355" spans="1:7" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A355" s="64"/>
+      <c r="B355" s="59" t="s">
         <v>509</v>
       </c>
-      <c r="C355" s="66">
+      <c r="C355" s="60">
         <v>41615</v>
       </c>
-      <c r="D355" s="66" t="s">
+      <c r="D355" s="60" t="s">
         <v>54</v>
       </c>
-      <c r="E355" s="66" t="s">
+      <c r="E355" s="60" t="s">
         <v>435</v>
       </c>
-      <c r="F355" s="71" t="s">
+      <c r="F355" s="65" t="s">
         <v>510</v>
       </c>
-      <c r="G355" s="69" t="s">
+      <c r="G355" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="356" spans="1:7" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A356" s="70"/>
-      <c r="B356" s="65" t="s">
+    <row r="356" spans="1:7" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A356" s="64"/>
+      <c r="B356" s="59" t="s">
         <v>511</v>
       </c>
-      <c r="C356" s="66">
+      <c r="C356" s="60">
         <v>42099</v>
       </c>
-      <c r="D356" s="66" t="s">
+      <c r="D356" s="60" t="s">
         <v>53</v>
       </c>
-      <c r="E356" s="66" t="s">
+      <c r="E356" s="60" t="s">
         <v>438</v>
       </c>
-      <c r="F356" s="71" t="s">
+      <c r="F356" s="65" t="s">
         <v>512</v>
       </c>
-      <c r="G356" s="69" t="s">
+      <c r="G356" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="357" spans="1:7" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A357" s="70"/>
-      <c r="B357" s="65" t="s">
+    <row r="357" spans="1:7" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A357" s="64"/>
+      <c r="B357" s="59" t="s">
         <v>513</v>
       </c>
-      <c r="C357" s="66">
+      <c r="C357" s="60">
         <v>44099</v>
       </c>
-      <c r="D357" s="66" t="s">
+      <c r="D357" s="60" t="s">
         <v>53</v>
       </c>
-      <c r="E357" s="66" t="s">
+      <c r="E357" s="60" t="s">
         <v>441</v>
       </c>
-      <c r="F357" s="71" t="s">
+      <c r="F357" s="65" t="s">
         <v>514</v>
       </c>
-      <c r="G357" s="69" t="s">
+      <c r="G357" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="358" spans="1:7" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A358" s="64">
+    <row r="358" spans="1:7" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A358" s="58">
         <v>98</v>
       </c>
-      <c r="B358" s="65" t="s">
+      <c r="B358" s="59" t="s">
         <v>515</v>
       </c>
-      <c r="C358" s="66">
+      <c r="C358" s="60">
         <v>38237</v>
       </c>
-      <c r="D358" s="66" t="s">
+      <c r="D358" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="E358" s="64">
+      <c r="E358" s="58">
         <v>98</v>
       </c>
-      <c r="F358" s="71" t="s">
+      <c r="F358" s="65" t="s">
         <v>516</v>
       </c>
-      <c r="G358" s="69" t="s">
+      <c r="G358" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="359" spans="1:7" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A359" s="64">
+    <row r="359" spans="1:7" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A359" s="58">
         <v>99</v>
       </c>
-      <c r="B359" s="73" t="s">
+      <c r="B359" s="67" t="s">
         <v>517</v>
       </c>
-      <c r="C359" s="66">
+      <c r="C359" s="60">
         <v>37544</v>
       </c>
-      <c r="D359" s="66" t="s">
+      <c r="D359" s="60" t="s">
         <v>518</v>
       </c>
-      <c r="E359" s="64">
+      <c r="E359" s="58">
         <v>99</v>
       </c>
-      <c r="F359" s="71" t="s">
+      <c r="F359" s="65" t="s">
         <v>519</v>
       </c>
-      <c r="G359" s="69" t="s">
+      <c r="G359" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="360" spans="1:7" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A360" s="70"/>
-      <c r="B360" s="65" t="s">
+    <row r="360" spans="1:7" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A360" s="64"/>
+      <c r="B360" s="59" t="s">
         <v>520</v>
       </c>
-      <c r="C360" s="66">
+      <c r="C360" s="60">
         <v>25166</v>
       </c>
-      <c r="D360" s="66" t="s">
+      <c r="D360" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="E360" s="66" t="s">
+      <c r="E360" s="60" t="s">
         <v>420</v>
       </c>
-      <c r="F360" s="71" t="s">
+      <c r="F360" s="65" t="s">
         <v>521</v>
       </c>
-      <c r="G360" s="69" t="s">
+      <c r="G360" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="361" spans="1:7" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A361" s="70"/>
-      <c r="B361" s="65" t="s">
+    <row r="361" spans="1:7" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A361" s="64"/>
+      <c r="B361" s="59" t="s">
         <v>522</v>
       </c>
-      <c r="C361" s="66">
+      <c r="C361" s="60">
         <v>24264</v>
       </c>
-      <c r="D361" s="66" t="s">
+      <c r="D361" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="E361" s="66" t="s">
+      <c r="E361" s="60" t="s">
         <v>423</v>
       </c>
-      <c r="F361" s="71" t="s">
+      <c r="F361" s="65" t="s">
         <v>523</v>
       </c>
-      <c r="G361" s="69" t="s">
+      <c r="G361" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="362" spans="1:7" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A362" s="64">
+    <row r="362" spans="1:7" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A362" s="58">
         <v>100</v>
       </c>
-      <c r="B362" s="65" t="s">
+      <c r="B362" s="59" t="s">
         <v>524</v>
       </c>
-      <c r="C362" s="66">
+      <c r="C362" s="60">
         <v>37967</v>
       </c>
-      <c r="D362" s="66" t="s">
+      <c r="D362" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="E362" s="64">
+      <c r="E362" s="58">
         <v>100</v>
       </c>
-      <c r="F362" s="71" t="s">
+      <c r="F362" s="65" t="s">
         <v>525</v>
       </c>
-      <c r="G362" s="69" t="s">
+      <c r="G362" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="363" spans="1:7" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A363" s="70"/>
-      <c r="B363" s="65" t="s">
+    <row r="363" spans="1:7" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A363" s="64"/>
+      <c r="B363" s="59" t="s">
         <v>526</v>
       </c>
-      <c r="C363" s="66">
+      <c r="C363" s="60">
         <v>24838</v>
       </c>
-      <c r="D363" s="66" t="s">
+      <c r="D363" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="E363" s="66" t="s">
+      <c r="E363" s="60" t="s">
         <v>420</v>
       </c>
-      <c r="F363" s="71" t="s">
+      <c r="F363" s="65" t="s">
         <v>527</v>
       </c>
-      <c r="G363" s="69" t="s">
+      <c r="G363" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="364" spans="1:7" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A364" s="70"/>
-      <c r="B364" s="65" t="s">
+    <row r="364" spans="1:7" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A364" s="64"/>
+      <c r="B364" s="59" t="s">
         <v>528</v>
       </c>
-      <c r="C364" s="66">
+      <c r="C364" s="60">
         <v>26167</v>
       </c>
-      <c r="D364" s="66" t="s">
+      <c r="D364" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="E364" s="66" t="s">
+      <c r="E364" s="60" t="s">
         <v>423</v>
       </c>
-      <c r="F364" s="71" t="s">
+      <c r="F364" s="65" t="s">
         <v>529</v>
       </c>
-      <c r="G364" s="69" t="s">
+      <c r="G364" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="365" spans="1:7" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A365" s="64">
+    <row r="365" spans="1:7" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A365" s="58">
         <v>101</v>
       </c>
-      <c r="B365" s="65" t="s">
+      <c r="B365" s="59" t="s">
         <v>530</v>
       </c>
-      <c r="C365" s="66">
+      <c r="C365" s="60">
         <v>31372</v>
       </c>
-      <c r="D365" s="66" t="s">
+      <c r="D365" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="E365" s="64">
+      <c r="E365" s="58">
         <v>101</v>
       </c>
-      <c r="F365" s="71" t="s">
+      <c r="F365" s="65" t="s">
         <v>531</v>
       </c>
-      <c r="G365" s="69" t="s">
+      <c r="G365" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="366" spans="1:7" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A366" s="70"/>
-      <c r="B366" s="73" t="s">
+    <row r="366" spans="1:7" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A366" s="64"/>
+      <c r="B366" s="67" t="s">
         <v>532</v>
       </c>
-      <c r="C366" s="66">
+      <c r="C366" s="60">
         <v>25187</v>
       </c>
-      <c r="D366" s="66" t="s">
+      <c r="D366" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="E366" s="66" t="s">
+      <c r="E366" s="60" t="s">
         <v>420</v>
       </c>
-      <c r="F366" s="71" t="s">
+      <c r="F366" s="65" t="s">
         <v>533</v>
       </c>
-      <c r="G366" s="69" t="s">
+      <c r="G366" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="367" spans="1:7" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A367" s="70"/>
-      <c r="B367" s="65" t="s">
+    <row r="367" spans="1:7" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A367" s="64"/>
+      <c r="B367" s="59" t="s">
         <v>534</v>
       </c>
-      <c r="C367" s="66">
+      <c r="C367" s="60">
         <v>35098</v>
       </c>
-      <c r="D367" s="66" t="s">
+      <c r="D367" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="E367" s="66" t="s">
+      <c r="E367" s="60" t="s">
         <v>423</v>
       </c>
-      <c r="F367" s="71" t="s">
+      <c r="F367" s="65" t="s">
         <v>535</v>
       </c>
-      <c r="G367" s="69" t="s">
+      <c r="G367" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="368" spans="1:7" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A368" s="70"/>
-      <c r="B368" s="65" t="s">
+    <row r="368" spans="1:7" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A368" s="64"/>
+      <c r="B368" s="59" t="s">
         <v>536</v>
       </c>
-      <c r="C368" s="66">
+      <c r="C368" s="60">
         <v>43182</v>
       </c>
-      <c r="D368" s="66" t="s">
+      <c r="D368" s="60" t="s">
         <v>53</v>
       </c>
-      <c r="E368" s="66" t="s">
+      <c r="E368" s="60" t="s">
         <v>432</v>
       </c>
-      <c r="F368" s="71" t="s">
+      <c r="F368" s="65" t="s">
         <v>537</v>
       </c>
-      <c r="G368" s="69" t="s">
+      <c r="G368" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="369" spans="1:7" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A369" s="70"/>
-      <c r="B369" s="65" t="s">
+    <row r="369" spans="1:7" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A369" s="64"/>
+      <c r="B369" s="59" t="s">
         <v>538</v>
       </c>
-      <c r="C369" s="66">
+      <c r="C369" s="60">
         <v>43974</v>
       </c>
-      <c r="D369" s="66" t="s">
+      <c r="D369" s="60" t="s">
         <v>54</v>
       </c>
-      <c r="E369" s="66" t="s">
+      <c r="E369" s="60" t="s">
         <v>435</v>
       </c>
-      <c r="F369" s="71" t="s">
+      <c r="F369" s="65" t="s">
         <v>539</v>
       </c>
-      <c r="G369" s="69" t="s">
+      <c r="G369" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="370" spans="1:7" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A370" s="70"/>
-      <c r="B370" s="65" t="s">
+    <row r="370" spans="1:7" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A370" s="64"/>
+      <c r="B370" s="59" t="s">
         <v>540</v>
       </c>
-      <c r="C370" s="66">
+      <c r="C370" s="60">
         <v>45261</v>
       </c>
-      <c r="D370" s="66" t="s">
+      <c r="D370" s="60" t="s">
         <v>54</v>
       </c>
-      <c r="E370" s="66" t="s">
+      <c r="E370" s="60" t="s">
         <v>438</v>
       </c>
-      <c r="F370" s="71" t="s">
+      <c r="F370" s="65" t="s">
         <v>541</v>
       </c>
-      <c r="G370" s="69" t="s">
+      <c r="G370" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="371" spans="1:7" ht="24" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="371" spans="1:7" ht="23.4" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A1:A259"/>
+  <autoFilter ref="A1:A259" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="9">
     <mergeCell ref="A311:I311"/>
     <mergeCell ref="A295:A297"/>
